--- a/rnaseq-with-probes/latest/rnaseq-with-probes.xlsx
+++ b/rnaseq-with-probes/latest/rnaseq-with-probes.xlsx
@@ -50,6 +50,11 @@
   <commentList>
     <comment ref="A1" authorId="1">
       <text>
+        <t>A styled paragraph describing the assay</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="1">
+      <text>
         <t>(Required) The unique identifier from HuBMAP or SenNet for the sample (such as a
 block, section, or suspension) used to perform the assay. For instance, in an
 RNAseq assay, the parent sample would be the suspension, while in imaging
@@ -58,7 +63,7 @@
 Example: HBM386.ZGKG.235, HBM672.MKPK.442</t>
       </text>
     </comment>
-    <comment ref="B1" authorId="1">
+    <comment ref="C1" authorId="1">
       <text>
         <t>A locally assigned identifier provided by the data provider for the dataset. It
 is used to reference an external metadata record that may be maintained
@@ -66,7 +71,7 @@
 Example: Visium_9OLC_A4_S1</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="1">
+    <comment ref="D1" authorId="1">
       <text>
         <t>(Required) The DOI for the protocols.io page that details the assay or the
 procedures used for sample procurement and preparation. For example, in the case
@@ -76,24 +81,24 @@
 Example: https://dx.doi.org/10.17504/protocols.io.eq2lyno9qvx9/v1</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="1">
+    <comment ref="E1" authorId="1">
       <text>
         <t>(Required) The specific type of dataset being produced. Example: RNAseq</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="1">
+    <comment ref="F1" authorId="1">
       <text>
         <t>(Required) The analyte class which is the target molecule that the assay is
 measuring. Example: DNA</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="1">
+    <comment ref="G1" authorId="1">
       <text>
         <t>(Required) Indicates whether a specific molecule or set of molecules is targeted
 for detection or measurement by the assay. Example: Yes</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="1">
+    <comment ref="H1" authorId="1">
       <text>
         <t>(Required) The company that manufactures or supplies the acquisition instrument.
 An acquisition instrument is a device equipped with signal detection hardware
@@ -103,7 +108,7 @@
 "In-House". Example: Illumina</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="I1" authorId="1">
       <text>
         <t>(Required) The specific model of the acquisition instrument, as manufacturers
 often offer various versions with differing features or sensitivities. These
@@ -112,7 +117,7 @@
 the model is unknown, enter "Unknown". Example: HiSeq 4000</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
+    <comment ref="J1" authorId="1">
       <text>
         <t>(Required) The length of time the sample was stored prior to processing it. For
 assays performed on tissue sections, this refers to how long the tissue section
@@ -121,32 +126,32 @@
 suspension was stored before library construction started. Example: 12</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="1">
+    <comment ref="K1" authorId="1">
       <text>
         <t>(Required) The unit of measurement used to specify the source storage duration
 value. Example: hour</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="1">
+    <comment ref="L1" authorId="1">
       <text>
         <t>The length of time since the acquisition instrument was last serviced or
 calibrated. This provides a metric for assessing drift in data capture. Example:
 10</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="1">
+    <comment ref="M1" authorId="1">
       <text>
         <t>The unit of measurement used to specify the time since acquisition instrument
 calibration value. Example: month</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="1">
+    <comment ref="N1" authorId="1">
       <text>
         <t>(Required) The name of the file containing the ORCID IDs for all contributors to
 this dataset. Example: ./contributors.csv</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="1">
+    <comment ref="O1" authorId="1">
       <text>
         <t>(Required) The top-level directory containing the raw and/or processed data. For
 a single dataset upload, this might be represented as ".", whereas for a data
@@ -158,7 +163,7 @@
 an internal metadata field used solely for data ingestion. Example: ./TEST001-RK</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="1">
+    <comment ref="P1" authorId="1">
       <text>
         <t>(Required) The position within a sequencing read where a barcode sequence
 begins. In sequencing libraries, barcodes—short DNA sequences used to tag
@@ -171,7 +176,7 @@
 Example: 0,38,76</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="1">
+    <comment ref="Q1" authorId="1">
       <text>
         <t>(Required) The sequencing read file contains the cell or capture spot barcode
 sequences. This information is essential when constructing sequencing libraries
@@ -180,13 +185,13 @@
 should be marked as "Not applicable". Example: Read 1 (R1)</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="1">
+    <comment ref="R1" authorId="1">
       <text>
         <t>(Required) The length of each cell or capture spot barcode in base pairs (bp).
 If the source material is not barcoded, enter "Not applicable". Example: 16</t>
       </text>
     </comment>
-    <comment ref="R1" authorId="1">
+    <comment ref="S1" authorId="1">
       <text>
         <t>(Required) The position within a sequencing read where the Unique Molecular
 Identifier (UMI) sequence begins. UMIs are short, random nucleotide sequences
@@ -194,34 +199,34 @@
 original molecule. If no UMI is used, enter "Not applicable". Example: 16</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="1">
+    <comment ref="T1" authorId="1">
       <text>
         <t>(Required) Specifies which sequencing read file contains the Unique Molecular
 Identifier (UMI) barcode. If no UMI is used, enter "Not applicable". Example:
 Read 1 (R1)</t>
       </text>
     </comment>
-    <comment ref="T1" authorId="1">
+    <comment ref="U1" authorId="1">
       <text>
         <t>(Required) The length of the Unique Molecular Identifier (UMI) in base pairs
 (bp). If no UMI is used, enter "Not applicable". Example: 8</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="1">
+    <comment ref="V1" authorId="1">
       <text>
         <t>(Required) The entity from which the analyte is captured. For example, in bulk
 sequencing, the source entity would be "tissue" while in single-cell sequencing,
 it would be "single cell". Example: single cell</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="1">
+    <comment ref="W1" authorId="1">
       <text>
         <t>The number of cells or nuclei that were input into the assay. This information
 is typically not available for assays performed on bulk tissue preparations, and
 therefore this field may be left blank. Example: 1000</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="1">
+    <comment ref="X1" authorId="1">
       <text>
         <t>The amount of RNA or DNA input into the assay, typically measured using
 instruments such as a Qubit, BioAnalyzer, or TapeStation. In most single-cell or
@@ -229,13 +234,13 @@
 field may be left blank. Example: 500</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="1">
+    <comment ref="Y1" authorId="1">
       <text>
         <t>The unit of measurement used to specify the amount of input analyte value. If no
 input amount, this field may be left blank. Example: ng</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="1">
+    <comment ref="Z1" authorId="1">
       <text>
         <t>(Required) The 5' and/or 3' adapter sequences used during library preparation to
 make the library compatible with the sequencing protocol and instrumentation.
@@ -244,57 +249,57 @@
 CTGTCTCTTATACACATCT</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="1">
+    <comment ref="AA1" authorId="1">
       <text>
         <t>(Required) The average size of sequencing library fragments, measured in base
 pairs (bp), as estimated by gel electrophoresis, BioAnalyzer, or TapeStation.
 Example: 200</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="1">
+    <comment ref="AB1" authorId="1">
       <text>
         <t>The amount of cDNA, after amplification, that was used for library construction.
 Example: 60</t>
       </text>
     </comment>
-    <comment ref="AB1" authorId="1">
+    <comment ref="AC1" authorId="1">
       <text>
         <t>The unit of measurement used to specify the library input amount value. Example:
 ng</t>
       </text>
     </comment>
-    <comment ref="AC1" authorId="1">
+    <comment ref="AD1" authorId="1">
       <text>
         <t>The total amount of library following the clean-up step after the final PCR
 amplification. To calculate, multiply the Qubit-measured concentration (ng/µl)
 by the elution volume (µl) obtained after the final clean-up. Example: 125</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="1">
+    <comment ref="AE1" authorId="1">
       <text>
         <t>The unit of measurement used to specify the library output amount value.
 Example: ng</t>
       </text>
     </comment>
-    <comment ref="AE1" authorId="1">
+    <comment ref="AF1" authorId="1">
       <text>
         <t>(Required) The concentration of the pooled library submitted for sequencing.
 Example: 2.5</t>
       </text>
     </comment>
-    <comment ref="AF1" authorId="1">
+    <comment ref="AG1" authorId="1">
       <text>
         <t>(Required) Unit of library concentration value.</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="1">
+    <comment ref="AH1" authorId="1">
       <text>
         <t>(Required) Indicates whether the sequencing library was prepared for single-end
 or paired-end sequencing. This information determines how reads are generated
 and aligned during data processing. Example: single-end</t>
       </text>
     </comment>
-    <comment ref="AH1" authorId="1">
+    <comment ref="AI1" authorId="1">
       <text>
         <t>(Required) The number of amplification cycles applied to cDNA prior to library
 construction. This is typically the number of PCR cycles used. For protocols
@@ -302,7 +307,7 @@
 amplification rounds performed. Example: 3</t>
       </text>
     </comment>
-    <comment ref="AI1" authorId="1">
+    <comment ref="AJ1" authorId="1">
       <text>
         <t>(Required) The number of PCR cycles used specifically to add sequencing adapters
 and amplify the library during the indexing step. This count does not include
@@ -310,7 +315,7 @@
 "Number of iterations of cDNA amplification" field. Example: 8</t>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="1">
+    <comment ref="AK1" authorId="1">
       <text>
         <t>The reagent kit used to construct the sequencing library, including both the kit
 name and, if available, version and product number. If the library was prepared
@@ -318,7 +323,7 @@
 GEM Single Cell 5' Kit v2, 16 rxns; PN 1000263</t>
       </text>
     </comment>
-    <comment ref="AK1" authorId="1">
+    <comment ref="AL1" authorId="1">
       <text>
         <t>The reagent kit used to add index sequences to samples. Indexes enable
 multiplexing, allowing multiple libraries to be pooled and sequenced together on
@@ -329,27 +334,27 @@
 "Not applicable". Example: 10X Genomics; Dual Index Kit TS, Set A; PN 1000251</t>
       </text>
     </comment>
-    <comment ref="AL1" authorId="1">
+    <comment ref="AM1" authorId="1">
       <text>
         <t>The specific sequencing barcode index set used, chosen from the sample indexing
 kit. For example, in the case of 10x, this might be "SI-GA-A1", whereas for
 Nextera, it could be "N505 - CTCCTTAC". Example: SI-GA-A1</t>
       </text>
     </comment>
-    <comment ref="AM1" authorId="1">
+    <comment ref="AN1" authorId="1">
       <text>
         <t>(Required) Indicates whether the sequencing reaction was run in replicate. If
 "Yes," the corresponding FASTQ files in the dataset should be merged for
 analysis. Example: Yes</t>
       </text>
     </comment>
-    <comment ref="AN1" authorId="1">
+    <comment ref="AO1" authorId="1">
       <text>
         <t>The number of cells, nuclei, or capture spots expected to be captured by the
 assay. Example: 14336</t>
       </text>
     </comment>
-    <comment ref="AO1" authorId="1">
+    <comment ref="AP1" authorId="1">
       <text>
         <t>(Required) The reagent kit used to perform the sequencing run, including the
 platform, kit name, version, and product number when available. If the reagent
@@ -357,14 +362,14 @@
 NextSeq 500/550 Hi Output Kit 150 Cycles; v2.5; PN 20024907</t>
       </text>
     </comment>
-    <comment ref="AP1" authorId="1">
+    <comment ref="AQ1" authorId="1">
       <text>
         <t>(Required) The number of sequencing cycles for each read and index in the
 sequencing run, typically reported as a comma-separated list in the order: Read
 1, i7 index, i5 index, and Read 2. Example: 50,8,16,50</t>
       </text>
     </comment>
-    <comment ref="AQ1" authorId="1">
+    <comment ref="AR1" authorId="1">
       <text>
         <t>A lab-assigned identifier for the sequencing run, such as a chip ID, that
 enables users to determine which samples were processed together. To avoid ID
@@ -372,7 +377,7 @@
 of the sequencing center. Example: Broad_Chip1234</t>
       </text>
     </comment>
-    <comment ref="AR1" authorId="1">
+    <comment ref="AS1" authorId="1">
       <text>
         <t>A lab-assigned identifier used to indicate which cells or nuclei were captured
 together in the same run. For example, in a 10X Genomics Chromium Controller
@@ -382,7 +387,7 @@
 the ID with the name of the sequencing center. Example: Broad_Batch1234</t>
       </text>
     </comment>
-    <comment ref="AS1" authorId="1">
+    <comment ref="AT1" authorId="1">
       <text>
         <t>The company that manufactures the instrument used to prepare the sample (e.g.,
 for staining or other processing steps) prior to the assay. If the instrument
@@ -390,7 +395,7 @@
 preparation occurred, enter "Not applicable". Example: 10X Genomics</t>
       </text>
     </comment>
-    <comment ref="AT1" authorId="1">
+    <comment ref="AU1" authorId="1">
       <text>
         <t>The specific model of the instrument used for sample preparation, such as
 staining. Manufacturers may offer multiple models with varying features or
@@ -399,7 +404,7 @@
 applicable". Example: Chromium X</t>
       </text>
     </comment>
-    <comment ref="AU1" authorId="1">
+    <comment ref="AV1" authorId="1">
       <text>
         <t>The reagent kit used in conjunction with the preparation instrument for sample
 processing (e.g., staining or labeling). If the reagent kit was prepared using a
@@ -407,20 +412,20 @@
 Single Cell Kit, 48 rxns; PN 1000120</t>
       </text>
     </comment>
-    <comment ref="AV1" authorId="1">
+    <comment ref="AW1" authorId="1">
       <text>
         <t>(Required) The duration for which the oligo-conjugated RNA or oligo-conjugated
 antibody probes were hybridized with the sample. Example: 30</t>
       </text>
     </comment>
-    <comment ref="AW1" authorId="1">
+    <comment ref="AX1" authorId="1">
       <text>
         <t>(Required) The unit of measurement for the probe hybridization time value. If
 the hybridization time is not specified, this field may be left blank. Example:
 minute</t>
       </text>
     </comment>
-    <comment ref="AX1" authorId="1">
+    <comment ref="AY1" authorId="1">
       <text>
         <t>(Required) The oligo probe panel used to target genes and/or proteins. If there
 is a core panel along with add-on modules, the core panel should be selected in
@@ -429,14 +434,14 @@
 Example: 10x Genomics; Visium Human Transcriptome Probe Kit-Small; PN 1000363</t>
       </text>
     </comment>
-    <comment ref="AY1" authorId="1">
+    <comment ref="AZ1" authorId="1">
       <text>
         <t>(Required) Indicates whether custom RNA or antibody probes were utilized in the
 assay. If custom probes were employed, they should be documented in the
 "custom_probe_set.csv" file. Example: No</t>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="1">
+    <comment ref="BA1" authorId="1">
       <text>
         <t>(Required) The unique string identifier for the metadata specification version,
 which is easily interpretable by computers for purposes of data validation and
@@ -448,7 +453,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="781">
+  <si>
+    <t>assay_description</t>
+  </si>
   <si>
     <t>parent_sample_id</t>
   </si>
@@ -636,6 +644,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000407</t>
   </si>
   <si>
+    <t>Illumina Spatial v0</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000487</t>
+  </si>
+  <si>
     <t>Olink</t>
   </si>
   <si>
@@ -1164,6 +1178,12 @@
     <t>https://identifiers.org/RRID:SCR_024569</t>
   </si>
   <si>
+    <t>LSM 710 Confocal Microscope</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_018063</t>
+  </si>
+  <si>
     <t>NanoZoomer 2.0-HT</t>
   </si>
   <si>
@@ -1884,6 +1904,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000366</t>
   </si>
   <si>
+    <t>10x Genomics; Chromium Next GEM Single Cell Fixed RNA Sample Preparation Kit, 16 rxns; PN 1000414</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000484</t>
+  </si>
+  <si>
     <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 4 slides, 16 reactions; PN 1000184</t>
   </si>
   <si>
@@ -2604,6 +2630,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000431</t>
   </si>
   <si>
+    <t>NanoString Technologies; GeoMx Human IO Proteome Atlas, 4 slides; PN 121300160</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000488</t>
+  </si>
+  <si>
     <t>10x Genomics; Chromium Fixed RNA Kit, Human Transcriptome 4 rxns x 4 BC; PN 1000475</t>
   </si>
   <si>
@@ -2757,7 +2789,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2026-02-23T13:18:56-08:00</t>
+    <t>2026-04-01T12:08:51-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -2816,11 +2848,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2883,61 +2916,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:BA2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" style="2" width="14.39453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" style="3" width="5.46875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" style="4" width="20.234375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" style="5" width="10.59765625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" style="6" width="10.9296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" style="7" width="9.40234375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" style="8" width="24.5546875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" style="9" width="24.0390625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" style="10" width="24.63671875" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" style="11" width="23.63671875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" style="12" width="41.1015625" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" style="13" width="40.1015625" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" style="14" width="14.5859375" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" style="15" width="8.46484375" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" style="16" width="12.27734375" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" style="17" width="11.26171875" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" style="18" width="10.9140625" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" style="19" width="9.01953125" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" style="20" width="8.00390625" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" style="21" width="7.65625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" style="22" width="15.00390625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" style="23" width="25.9765625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" style="24" width="24.99609375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" style="25" width="23.99609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" style="26" width="20.4609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" style="27" width="24.20703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" style="28" width="22.0703125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" style="29" width="21.0703125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" style="30" width="23.17578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" style="31" width="22.17578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" style="32" width="21.9453125" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" style="33" width="20.9453125" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" style="34" width="11.296875" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" style="35" width="34.82421875" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" style="36" width="28.32421875" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" style="37" width="18.2734375" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" style="38" width="16.65234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" style="39" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" style="40" width="17.18359375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" style="41" width="24.72265625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" style="42" width="19.05859375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" style="43" width="19.78125" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" style="44" width="16.94921875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" style="45" width="13.96484375" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" style="46" width="25.0859375" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" style="47" width="24.57421875" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" style="48" width="21.765625" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" style="49" width="25.3203125" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" style="50" width="24.3203125" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" style="51" width="15.00390625" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" style="52" width="19.1328125" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" style="53" width="16.91796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" style="2" width="14.46875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="2" max="2" style="3" width="14.39453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" style="4" width="5.46875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" style="5" width="20.234375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" style="6" width="10.59765625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" style="7" width="10.9296875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" style="8" width="9.40234375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" style="9" width="24.5546875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" style="10" width="24.0390625" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" style="11" width="24.63671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" style="12" width="23.63671875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" style="13" width="41.1015625" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" style="14" width="40.1015625" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" style="15" width="14.5859375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" style="16" width="8.46484375" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" style="17" width="12.27734375" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" style="18" width="11.26171875" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" style="19" width="10.9140625" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" style="20" width="9.01953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" style="21" width="8.00390625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" style="22" width="7.65625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" style="23" width="15.00390625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" style="24" width="25.9765625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" style="25" width="24.99609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" style="26" width="23.99609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" style="27" width="20.4609375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" style="28" width="24.20703125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" style="29" width="22.0703125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" style="30" width="21.0703125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" style="31" width="23.17578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" style="32" width="22.17578125" customWidth="true" bestFit="true"/>
+    <col min="32" max="32" style="33" width="21.9453125" customWidth="true" bestFit="true"/>
+    <col min="33" max="33" style="34" width="20.9453125" customWidth="true" bestFit="true"/>
+    <col min="34" max="34" style="35" width="11.296875" customWidth="true" bestFit="true"/>
+    <col min="35" max="35" style="36" width="34.82421875" customWidth="true" bestFit="true"/>
+    <col min="36" max="36" style="37" width="28.32421875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" style="38" width="18.2734375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" style="39" width="16.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" style="40" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" style="41" width="17.18359375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" style="42" width="24.72265625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" style="43" width="19.05859375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" style="44" width="19.78125" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" style="45" width="16.94921875" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" style="46" width="13.96484375" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" style="47" width="25.0859375" customWidth="true" bestFit="true"/>
+    <col min="47" max="47" style="48" width="24.57421875" customWidth="true" bestFit="true"/>
+    <col min="48" max="48" style="49" width="21.765625" customWidth="true" bestFit="true"/>
+    <col min="49" max="49" style="50" width="25.3203125" customWidth="true" bestFit="true"/>
+    <col min="50" max="50" style="51" width="24.3203125" customWidth="true" bestFit="true"/>
+    <col min="51" max="51" style="52" width="15.00390625" customWidth="true" bestFit="true"/>
+    <col min="52" max="52" style="53" width="19.1328125" customWidth="true" bestFit="true"/>
+    <col min="53" max="53" style="54" width="16.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2954,293 +2988,296 @@
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="G1" t="s" s="1">
         <v>154</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>389</v>
+        <v>224</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="Q1" t="s" s="1">
         <v>419</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="Y1" t="s" s="1">
         <v>450</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AH1" t="s" s="1">
         <v>471</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>548</v>
+        <v>478</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>583</v>
+        <v>555</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>643</v>
+        <v>593</v>
       </c>
       <c r="AQ1" t="s" s="1">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="AR1" t="s" s="1">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="AS1" t="s" s="1">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="AT1" t="s" s="1">
         <v>653</v>
       </c>
       <c r="AU1" t="s" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="AV1" t="s" s="1">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="AW1" t="s" s="1">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="AX1" t="s" s="1">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="AY1" t="s" s="1">
-        <v>762</v>
+        <v>710</v>
       </c>
       <c r="AZ1" t="s" s="1">
-        <v>763</v>
+        <v>771</v>
+      </c>
+      <c r="BA1" t="s" s="1">
+        <v>772</v>
       </c>
     </row>
     <row r="2">
-      <c r="D2" t="s" s="5">
-        <v>106</v>
-      </c>
-      <c r="AZ2" t="s" s="53">
-        <v>764</v>
+      <c r="E2" t="s" s="6">
+        <v>109</v>
+      </c>
+      <c r="BA2" t="s" s="54">
+        <v>773</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="41">
-    <dataValidation type="list" sqref="D2:D1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'dataset_type'!$A$1:$A$55</formula1>
+    <dataValidation type="list" sqref="E2:E1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+      <formula1>'dataset_type'!$A$1:$A$56</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E2:E1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="F2:F1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'analyte_class'!$A$1:$A$18</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F2:F1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="G2:G1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'is_targeted'!$A$1:$A$2</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G2:G1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="H2:H1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'acquisition_instrument_vendor'!$A$1:$A$33</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'acquisition_instrument_model'!$A$1:$A$85</formula1>
+    <dataValidation type="list" sqref="I2:I1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+      <formula1>'acquisition_instrument_model'!$A$1:$A$86</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="I2:I1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="J2:J1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
       <formula1>0</formula1>
       <formula2/>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:J1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="K2:K1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'source_storage_duration_unit'!$A$1:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="K2:K1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="L2:L1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
       <formula1>0</formula1>
       <formula2/>
     </dataValidation>
-    <dataValidation type="list" sqref="L2:L1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="M2:M1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'time_since_acquisition_instrume'!$A$1:$A$3</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="O2:O1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="P2:P1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'barcode_offset'!$A$1:$A$9</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="P2:P1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="Q2:Q1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'barcode_read'!$A$1:$A$3</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="Q2:Q1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="R2:R1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'barcode_size'!$A$1:$A$6</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="R2:R1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="S2:S1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'umi_offset'!$A$1:$A$4</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="S2:S1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="T2:T1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'umi_read'!$A$1:$A$3</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="T2:T1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="U2:U1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'umi_size'!$A$1:$A$6</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="U2:U1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="V2:V1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'assay_input_entity'!$A$1:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" sqref="V2:V1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="whole" operator="between" sqref="W2:W1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" sqref="W2:W1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="decimal" operator="between" sqref="X2:X1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-3.4028235E38</formula1>
       <formula2>3.4028235E38</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="X2:X1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="Y2:Y1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'amount_of_input_analyte_unit'!$A$1:$A$2</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" sqref="Z2:Z1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="whole" operator="between" sqref="AA2:AA1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" sqref="AA2:AA1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="decimal" operator="between" sqref="AB2:AB1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-3.4028235E38</formula1>
       <formula2>3.4028235E38</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="AB2:AB1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AC2:AC1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'library_input_amount_unit'!$A$1:$A$2</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" sqref="AC2:AC1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="decimal" operator="between" sqref="AD2:AD1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-3.4028235E38</formula1>
       <formula2>3.4028235E38</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="AD2:AD1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AE2:AE1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'library_output_amount_unit'!$A$1:$A$2</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" sqref="AE2:AE1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="decimal" operator="between" sqref="AF2:AF1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-3.4028235E38</formula1>
       <formula2>3.4028235E38</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="AF2:AF1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AG2:AG1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'library_concentration_unit'!$A$1:$A$3</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AG2:AG1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AH2:AH1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'library_layout'!$A$1:$A$2</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" sqref="AH2:AH1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
-      <formula1>-2147483648</formula1>
-      <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation type="whole" operator="between" sqref="AI2:AI1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="AJ2:AJ1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'library_preparation_kit'!$A$1:$A$37</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="AK2:AK1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'sample_indexing_kit'!$A$1:$A$19</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="AM2:AM1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'is_technical_replicate'!$A$1:$A$2</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" sqref="AN2:AN1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="whole" operator="between" sqref="AJ2:AJ1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="AO2:AO1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AK2:AK1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+      <formula1>'library_preparation_kit'!$A$1:$A$38</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="AL2:AL1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+      <formula1>'sample_indexing_kit'!$A$1:$A$19</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="AN2:AN1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+      <formula1>'is_technical_replicate'!$A$1:$A$2</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" sqref="AO2:AO1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+      <formula1>-2147483648</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation type="list" sqref="AP2:AP1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'sequencing_reagent_kit'!$A$1:$A$29</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AS2:AS1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AT2:AT1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'preparation_instrument_vendor'!$A$1:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AT2:AT1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AU2:AU1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'preparation_instrument_model'!$A$1:$A$19</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AU2:AU1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AV2:AV1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'preparation_instrument_kit'!$A$1:$A$13</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" sqref="AV2:AV1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="decimal" operator="between" sqref="AW2:AW1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-3.4028235E38</formula1>
       <formula2>3.4028235E38</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="AW2:AW1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AX2:AX1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'probe_hybridization_time_unit'!$A$1:$A$2</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AX2:AX1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'oligo_probe_panel'!$A$1:$A$30</formula1>
+    <dataValidation type="list" sqref="AY2:AY1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+      <formula1>'oligo_probe_panel'!$A$1:$A$31</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AY2:AY1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AZ2:AZ1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'is_custom_probes_used'!$A$1:$A$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -3257,26 +3294,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -3291,32 +3328,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -3331,22 +3368,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -3361,26 +3398,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -3395,32 +3432,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -3435,42 +3472,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -3485,18 +3522,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -3511,18 +3548,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -3537,18 +3574,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -3563,26 +3600,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -3592,447 +3629,455 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>113</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -4047,18 +4092,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -4068,303 +4113,311 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>533</v>
+        <v>538</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>545</v>
+        <v>550</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>547</v>
+        <v>552</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>553</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -4379,154 +4432,154 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>552</v>
+        <v>559</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>558</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>560</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>562</v>
+        <v>569</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>566</v>
+        <v>573</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>568</v>
+        <v>575</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>570</v>
+        <v>577</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>572</v>
+        <v>579</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>574</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>576</v>
+        <v>583</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>580</v>
+        <v>587</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -4541,12 +4594,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -4561,234 +4614,234 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>588</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>590</v>
+        <v>597</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>592</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>594</v>
+        <v>601</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>596</v>
+        <v>603</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>600</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>602</v>
+        <v>609</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>604</v>
+        <v>611</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>606</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>608</v>
+        <v>615</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>610</v>
+        <v>617</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>612</v>
+        <v>619</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>614</v>
+        <v>621</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>618</v>
+        <v>625</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>620</v>
+        <v>627</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>624</v>
+        <v>631</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>626</v>
+        <v>633</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>628</v>
+        <v>635</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>630</v>
+        <v>637</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>632</v>
+        <v>639</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>634</v>
+        <v>641</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>636</v>
+        <v>643</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>638</v>
+        <v>645</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>640</v>
+        <v>647</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>642</v>
+        <v>649</v>
       </c>
     </row>
   </sheetData>
@@ -4803,90 +4856,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>648</v>
+        <v>655</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>650</v>
+        <v>657</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>652</v>
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -4901,154 +4954,154 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>655</v>
+        <v>662</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>657</v>
+        <v>664</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>661</v>
+        <v>668</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>663</v>
+        <v>670</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>665</v>
+        <v>672</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>667</v>
+        <v>674</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>669</v>
+        <v>676</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>671</v>
+        <v>678</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>673</v>
+        <v>680</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>675</v>
+        <v>682</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>677</v>
+        <v>684</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>679</v>
+        <v>686</v>
       </c>
     </row>
   </sheetData>
@@ -5063,106 +5116,106 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>682</v>
+        <v>689</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>686</v>
+        <v>693</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>688</v>
+        <v>695</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>690</v>
+        <v>697</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>692</v>
+        <v>699</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>694</v>
+        <v>701</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>541</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>696</v>
+        <v>703</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>698</v>
+        <v>705</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>700</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
@@ -5177,18 +5230,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -5198,247 +5251,255 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>705</v>
+        <v>712</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>709</v>
+        <v>716</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>711</v>
+        <v>718</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>713</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>715</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>717</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>719</v>
+        <v>726</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>721</v>
+        <v>728</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>725</v>
+        <v>732</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>727</v>
+        <v>734</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>729</v>
+        <v>736</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>731</v>
+        <v>738</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>733</v>
+        <v>740</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>735</v>
+        <v>742</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>737</v>
+        <v>744</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>739</v>
+        <v>746</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>743</v>
+        <v>750</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>745</v>
+        <v>752</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>747</v>
+        <v>754</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>530</v>
+        <v>755</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>531</v>
+        <v>756</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>748</v>
+        <v>537</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>749</v>
+        <v>538</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>751</v>
+        <v>758</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>753</v>
+        <v>760</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>755</v>
+        <v>762</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>757</v>
+        <v>764</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>759</v>
+        <v>766</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>761</v>
+        <v>768</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>769</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -5453,146 +5514,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -5607,12 +5668,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -5633,30 +5694,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>770</v>
+        <v>779</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>771</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -5671,12 +5732,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -5691,266 +5752,266 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -5960,687 +6021,695 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>74</v>
+        <v>355</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>353</v>
+        <v>77</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>187</v>
+        <v>362</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>188</v>
+        <v>363</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>359</v>
+        <v>190</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>360</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>388</v>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>392</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -6655,42 +6724,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -6705,26 +6774,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -6739,47 +6808,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/rnaseq-with-probes/latest/rnaseq-with-probes.xlsx
+++ b/rnaseq-with-probes/latest/rnaseq-with-probes.xlsx
@@ -453,7 +453,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="785">
   <si>
     <t>assay_description</t>
   </si>
@@ -644,102 +644,108 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000407</t>
   </si>
   <si>
-    <t>Illumina Spatial v0</t>
+    <t>Olink</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000441</t>
+  </si>
+  <si>
+    <t>MIBI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000172</t>
+  </si>
+  <si>
+    <t>Auto-fluorescence</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000205</t>
+  </si>
+  <si>
+    <t>FACS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000440</t>
+  </si>
+  <si>
+    <t>Xenium</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000219</t>
+  </si>
+  <si>
+    <t>DNA Methylation</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000490</t>
+  </si>
+  <si>
+    <t>SIMS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000202</t>
+  </si>
+  <si>
+    <t>Cell DIVE</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000159</t>
+  </si>
+  <si>
+    <t>CODEX</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000160</t>
+  </si>
+  <si>
+    <t>GeoMx (NGS)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000300</t>
+  </si>
+  <si>
+    <t>MUSIC</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000328</t>
+  </si>
+  <si>
+    <t>Pixel-seqV2</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000450</t>
+  </si>
+  <si>
+    <t>MALDI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000201</t>
+  </si>
+  <si>
+    <t>2D Imaging Mass Cytometry</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000296</t>
+  </si>
+  <si>
+    <t>Histology</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000197</t>
+  </si>
+  <si>
+    <t>Enhanced Stimulated Raman Spectroscopy (SRS)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000209</t>
+  </si>
+  <si>
+    <t>Illumina Spatial ver0</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000487</t>
   </si>
   <si>
-    <t>Olink</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000441</t>
-  </si>
-  <si>
-    <t>MIBI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000172</t>
-  </si>
-  <si>
-    <t>Auto-fluorescence</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000205</t>
-  </si>
-  <si>
-    <t>FACS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000440</t>
-  </si>
-  <si>
-    <t>Xenium</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000219</t>
-  </si>
-  <si>
-    <t>SIMS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000202</t>
-  </si>
-  <si>
-    <t>Cell DIVE</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000159</t>
-  </si>
-  <si>
-    <t>CODEX</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000160</t>
-  </si>
-  <si>
-    <t>GeoMx (NGS)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000300</t>
-  </si>
-  <si>
-    <t>MUSIC</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000328</t>
-  </si>
-  <si>
-    <t>Pixel-seqV2</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000450</t>
-  </si>
-  <si>
-    <t>MALDI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000201</t>
-  </si>
-  <si>
-    <t>2D Imaging Mass Cytometry</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000296</t>
-  </si>
-  <si>
-    <t>Histology</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000197</t>
-  </si>
-  <si>
-    <t>Enhanced Stimulated Raman Spectroscopy (SRS)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000209</t>
-  </si>
-  <si>
     <t>DART-FISH</t>
   </si>
   <si>
@@ -1553,6 +1559,12 @@
     <t>https://identifiers.org/RRID:SCR_016386</t>
   </si>
   <si>
+    <t>Q Exactive HF-X</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020564</t>
+  </si>
+  <si>
     <t>solariX</t>
   </si>
   <si>
@@ -2636,12 +2648,6 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000488</t>
   </si>
   <si>
-    <t>10x Genomics; Chromium Fixed RNA Kit, Human Transcriptome 4 rxns x 4 BC; PN 1000475</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000307</t>
-  </si>
-  <si>
     <t>10x Genomics; Visium Human Transcriptome Probe Kit v2 - Small; PN 1000466</t>
   </si>
   <si>
@@ -2750,6 +2756,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000306</t>
   </si>
   <si>
+    <t>10x Genomics; Xenium Human Skin Gene Expression Panel; PN 1000643</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000491</t>
+  </si>
+  <si>
     <t>NanoString Technologies; CosMx Human Universal Cell Characterization Panel (RNA, 1000 Plex); PN CMX-H-USCP-1KP-R</t>
   </si>
   <si>
@@ -2789,7 +2801,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2026-04-01T12:08:51-07:00</t>
+    <t>2026-06-11T13:19:37-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -2991,162 +3003,162 @@
         <v>4</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="AQ1" t="s" s="1">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="AR1" t="s" s="1">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="AS1" t="s" s="1">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="AT1" t="s" s="1">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="AU1" t="s" s="1">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="AV1" t="s" s="1">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="AW1" t="s" s="1">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="AX1" t="s" s="1">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="AY1" t="s" s="1">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="AZ1" t="s" s="1">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="BA1" t="s" s="1">
-        <v>772</v>
+        <v>776</v>
       </c>
     </row>
     <row r="2">
       <c r="E2" t="s" s="6">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BA2" t="s" s="54">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="41">
     <dataValidation type="list" sqref="E2:E1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'dataset_type'!$A$1:$A$56</formula1>
+      <formula1>'dataset_type'!$A$1:$A$57</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F2:F1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'analyte_class'!$A$1:$A$18</formula1>
@@ -3158,7 +3170,7 @@
       <formula1>'acquisition_instrument_vendor'!$A$1:$A$33</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I2:I1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'acquisition_instrument_model'!$A$1:$A$86</formula1>
+      <formula1>'acquisition_instrument_model'!$A$1:$A$87</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="J2:J1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
       <formula1>0</formula1>
@@ -3294,26 +3306,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -3328,32 +3340,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3368,22 +3380,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3398,26 +3410,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -3432,32 +3444,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3472,42 +3484,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -3522,18 +3534,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -3548,18 +3560,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -3574,18 +3586,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -3600,26 +3612,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -3629,7 +3641,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4078,6 +4090,14 @@
       </c>
       <c r="B56" t="s" s="0">
         <v>116</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -4092,18 +4112,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -4118,306 +4138,306 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -4432,154 +4452,154 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -4594,12 +4614,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -4614,234 +4634,234 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>597</v>
+        <v>601</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -4856,90 +4876,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>
@@ -4954,154 +4974,154 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -5116,106 +5136,106 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>691</v>
+        <v>695</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>699</v>
+        <v>703</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>705</v>
+        <v>709</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>
@@ -5230,18 +5250,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -5256,250 +5276,250 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>726</v>
+        <v>730</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>730</v>
+        <v>734</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>734</v>
+        <v>738</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>736</v>
+        <v>740</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>738</v>
+        <v>742</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>755</v>
+        <v>541</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>756</v>
+        <v>542</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>537</v>
+        <v>759</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>538</v>
+        <v>760</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>758</v>
+        <v>762</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
   </sheetData>
@@ -5514,146 +5534,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -5668,12 +5688,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -5694,30 +5714,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>779</v>
+        <v>783</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>780</v>
+        <v>784</v>
       </c>
     </row>
   </sheetData>
@@ -5732,12 +5752,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -5752,266 +5772,266 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -6021,535 +6041,535 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B86"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="67">
@@ -6557,159 +6577,167 @@
         <v>77</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>393</v>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>396</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -6724,42 +6752,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -6774,26 +6802,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -6808,47 +6836,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/rnaseq-with-probes/latest/rnaseq-with-probes.xlsx
+++ b/rnaseq-with-probes/latest/rnaseq-with-probes.xlsx
@@ -453,7 +453,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="795">
   <si>
     <t>assay_description</t>
   </si>
@@ -794,6 +794,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000311</t>
   </si>
   <si>
+    <t>Paired-Tag</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000492</t>
+  </si>
+  <si>
     <t>MS Lipidomics</t>
   </si>
   <si>
@@ -2543,6 +2549,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000462</t>
   </si>
   <si>
+    <t>10x Genomics; Visium HD, Mouse Transcriptome, 6.5 mm, 4 runs; PN 1000676</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000494</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 48 rxns; PN 1000286</t>
   </si>
   <si>
@@ -2561,6 +2573,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000378</t>
   </si>
   <si>
+    <t>10x Genomics; Visium HD, Human Transcriptome, 6.5 mm, 4 runs; PN 1000675</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000493</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 16 rxns; PN 1000287</t>
   </si>
   <si>
@@ -2573,6 +2591,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000379</t>
   </si>
   <si>
+    <t>10x Genomics; Visium HD, Human Transcriptome, 11 mm, 4 runs; PN 1001037</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000495</t>
+  </si>
+  <si>
     <t>10x Genomics; Chromium GEM-X Single Cell 3' Kit v4, 16 rxns; PN 1000691</t>
   </si>
   <si>
@@ -2591,6 +2615,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000325</t>
   </si>
   <si>
+    <t>10x Genomics; Visium HD, Mouse Transcriptome, 11 mm, 4 runs; PN 1001038</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000496</t>
+  </si>
+  <si>
     <t>probe_hybridization_time_value</t>
   </si>
   <si>
@@ -2801,7 +2831,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2026-06-11T13:19:37-07:00</t>
+    <t>2026-06-29T15:47:17-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -3003,148 +3033,148 @@
         <v>4</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AQ1" t="s" s="1">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AR1" t="s" s="1">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AS1" t="s" s="1">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AT1" t="s" s="1">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AU1" t="s" s="1">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AV1" t="s" s="1">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AW1" t="s" s="1">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="AX1" t="s" s="1">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="AY1" t="s" s="1">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="AZ1" t="s" s="1">
-        <v>775</v>
+        <v>785</v>
       </c>
       <c r="BA1" t="s" s="1">
-        <v>776</v>
+        <v>786</v>
       </c>
     </row>
     <row r="2">
@@ -3152,13 +3182,13 @@
         <v>111</v>
       </c>
       <c r="BA2" t="s" s="54">
-        <v>777</v>
+        <v>787</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="41">
     <dataValidation type="list" sqref="E2:E1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'dataset_type'!$A$1:$A$57</formula1>
+      <formula1>'dataset_type'!$A$1:$A$58</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F2:F1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'analyte_class'!$A$1:$A$18</formula1>
@@ -3277,7 +3307,7 @@
       <formula1>'preparation_instrument_model'!$A$1:$A$19</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AV2:AV1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'preparation_instrument_kit'!$A$1:$A$13</formula1>
+      <formula1>'preparation_instrument_kit'!$A$1:$A$17</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" sqref="AW2:AW1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-3.4028235E38</formula1>
@@ -3306,26 +3336,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -3340,32 +3370,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3380,22 +3410,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3410,26 +3440,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -3444,32 +3474,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3484,42 +3514,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -3534,18 +3564,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -3560,18 +3590,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -3586,18 +3616,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -3612,26 +3642,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -3641,7 +3671,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4098,6 +4128,14 @@
       </c>
       <c r="B57" t="s" s="0">
         <v>118</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -4112,18 +4150,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -4138,306 +4176,306 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -4452,154 +4490,154 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -4614,12 +4652,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -4634,234 +4672,234 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>
@@ -4876,90 +4914,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -4974,154 +5012,154 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -5131,111 +5169,143 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>541</v>
+        <v>704</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>542</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>702</v>
+        <v>543</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>703</v>
+        <v>544</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>551</v>
+        <v>708</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>552</v>
+        <v>709</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>708</v>
+        <v>553</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>709</v>
+        <v>554</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>711</v>
+        <v>713</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>714</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>716</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>718</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>720</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>721</v>
       </c>
     </row>
   </sheetData>
@@ -5250,18 +5320,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -5276,250 +5346,250 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>716</v>
+        <v>726</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>718</v>
+        <v>728</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>720</v>
+        <v>730</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>722</v>
+        <v>732</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>724</v>
+        <v>734</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>726</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>728</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>729</v>
+        <v>739</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>730</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>732</v>
+        <v>742</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>733</v>
+        <v>743</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>734</v>
+        <v>744</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>736</v>
+        <v>746</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>738</v>
+        <v>748</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>740</v>
+        <v>750</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>741</v>
+        <v>751</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>742</v>
+        <v>752</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>744</v>
+        <v>754</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>746</v>
+        <v>756</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>747</v>
+        <v>757</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>748</v>
+        <v>758</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>750</v>
+        <v>760</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>752</v>
+        <v>762</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>753</v>
+        <v>763</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>754</v>
+        <v>764</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>755</v>
+        <v>765</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>756</v>
+        <v>766</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>757</v>
+        <v>767</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>758</v>
+        <v>768</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>759</v>
+        <v>769</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>760</v>
+        <v>770</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>761</v>
+        <v>771</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>762</v>
+        <v>772</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>764</v>
+        <v>774</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>765</v>
+        <v>775</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>766</v>
+        <v>776</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>768</v>
+        <v>778</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>770</v>
+        <v>780</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>771</v>
+        <v>781</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>772</v>
+        <v>782</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>773</v>
+        <v>783</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>774</v>
+        <v>784</v>
       </c>
     </row>
   </sheetData>
@@ -5534,146 +5604,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -5688,12 +5758,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -5714,16 +5784,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>778</v>
+        <v>788</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>779</v>
+        <v>789</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>781</v>
+        <v>791</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>783</v>
+        <v>793</v>
       </c>
     </row>
     <row r="2">
@@ -5731,13 +5801,13 @@
         <v>111</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>782</v>
+        <v>792</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>784</v>
+        <v>794</v>
       </c>
     </row>
   </sheetData>
@@ -5752,12 +5822,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -5772,266 +5842,266 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -6046,530 +6116,530 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="67">
@@ -6577,167 +6647,167 @@
         <v>77</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B87" t="s" s="0">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -6752,42 +6822,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -6802,26 +6872,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -6836,47 +6906,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/rnaseq-with-probes/latest/rnaseq-with-probes.xlsx
+++ b/rnaseq-with-probes/latest/rnaseq-with-probes.xlsx
@@ -453,7 +453,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="801">
   <si>
     <t>assay_description</t>
   </si>
@@ -1184,6 +1184,12 @@
     <t>https://identifiers.org/RRID:SCR_025070</t>
   </si>
   <si>
+    <t>Orbitrap Astral</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_028684</t>
+  </si>
+  <si>
     <t>NovaSeq X</t>
   </si>
   <si>
@@ -2126,6 +2132,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000338</t>
   </si>
   <si>
+    <t>10x Genomics; GEM-X Flex GEM &amp; Library Kit, 4 rxns; PN 1000782</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000497</t>
+  </si>
+  <si>
     <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 8 rxns; PN 1000374</t>
   </si>
   <si>
@@ -2615,6 +2627,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000325</t>
   </si>
   <si>
+    <t>10x Genomics; GEM-X Flex Gene Expression Chip Kit, 4 chips; PN 1000791</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000498</t>
+  </si>
+  <si>
     <t>10x Genomics; Visium HD, Mouse Transcriptome, 11 mm, 4 runs; PN 1001038</t>
   </si>
   <si>
@@ -2831,7 +2849,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2026-06-29T15:47:17-07:00</t>
+    <t>2026-07-17T10:23:51-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -3045,136 +3063,136 @@
         <v>228</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AQ1" t="s" s="1">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="AR1" t="s" s="1">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="AS1" t="s" s="1">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="AT1" t="s" s="1">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="AU1" t="s" s="1">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="AV1" t="s" s="1">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="AW1" t="s" s="1">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="AX1" t="s" s="1">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="AY1" t="s" s="1">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="AZ1" t="s" s="1">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="BA1" t="s" s="1">
-        <v>786</v>
+        <v>792</v>
       </c>
     </row>
     <row r="2">
@@ -3182,7 +3200,7 @@
         <v>111</v>
       </c>
       <c r="BA2" t="s" s="54">
-        <v>787</v>
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -3200,7 +3218,7 @@
       <formula1>'acquisition_instrument_vendor'!$A$1:$A$33</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I2:I1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'acquisition_instrument_model'!$A$1:$A$87</formula1>
+      <formula1>'acquisition_instrument_model'!$A$1:$A$88</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="J2:J1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
       <formula1>0</formula1>
@@ -3285,7 +3303,7 @@
       <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation type="list" sqref="AK2:AK1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'library_preparation_kit'!$A$1:$A$38</formula1>
+      <formula1>'library_preparation_kit'!$A$1:$A$39</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AL2:AL1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'sample_indexing_kit'!$A$1:$A$19</formula1>
@@ -3307,7 +3325,7 @@
       <formula1>'preparation_instrument_model'!$A$1:$A$19</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AV2:AV1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'preparation_instrument_kit'!$A$1:$A$17</formula1>
+      <formula1>'preparation_instrument_kit'!$A$1:$A$18</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" sqref="AW2:AW1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-3.4028235E38</formula1>
@@ -3336,10 +3354,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2">
@@ -3352,10 +3370,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -3370,27 +3388,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6">
@@ -3410,17 +3428,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4">
@@ -3440,10 +3458,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2">
@@ -3456,10 +3474,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -3474,27 +3492,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6">
@@ -3514,42 +3532,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>
@@ -3564,18 +3582,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -3590,18 +3608,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -3616,18 +3634,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -3642,26 +3660,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -4150,18 +4168,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -4171,311 +4189,319 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>560</v>
+        <v>562</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>563</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>564</v>
       </c>
     </row>
   </sheetData>
@@ -4490,18 +4516,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3">
@@ -4514,130 +4540,130 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -4672,234 +4698,234 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -4946,18 +4972,18 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="7">
@@ -4994,10 +5020,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -5012,10 +5038,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2">
@@ -5028,10 +5054,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="4">
@@ -5044,122 +5070,122 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>692</v>
+        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -5169,143 +5195,151 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>699</v>
+        <v>703</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>705</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>711</v>
+        <v>715</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>715</v>
+        <v>719</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>717</v>
+        <v>721</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>721</v>
+        <v>725</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>726</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>727</v>
       </c>
     </row>
   </sheetData>
@@ -5320,18 +5354,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -5346,250 +5380,250 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>726</v>
+        <v>732</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>728</v>
+        <v>734</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>730</v>
+        <v>736</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>732</v>
+        <v>738</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>734</v>
+        <v>740</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>740</v>
+        <v>746</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>744</v>
+        <v>750</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>746</v>
+        <v>752</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>748</v>
+        <v>754</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>750</v>
+        <v>756</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>752</v>
+        <v>758</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>754</v>
+        <v>760</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>756</v>
+        <v>762</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>758</v>
+        <v>764</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>762</v>
+        <v>768</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>764</v>
+        <v>770</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>766</v>
+        <v>772</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>768</v>
+        <v>774</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>770</v>
+        <v>776</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>772</v>
+        <v>778</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>774</v>
+        <v>780</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>776</v>
+        <v>782</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>778</v>
+        <v>784</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>780</v>
+        <v>786</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>782</v>
+        <v>788</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>784</v>
+        <v>790</v>
       </c>
     </row>
   </sheetData>
@@ -5784,16 +5818,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>793</v>
+        <v>799</v>
       </c>
     </row>
     <row r="2">
@@ -5801,13 +5835,13 @@
         <v>111</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>794</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -6111,7 +6145,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6644,15 +6678,15 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="B68" t="s" s="0">
         <v>363</v>
@@ -6676,18 +6710,18 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>194</v>
+        <v>368</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>195</v>
+        <v>369</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>368</v>
+        <v>194</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>369</v>
+        <v>195</v>
       </c>
     </row>
     <row r="73">
@@ -6808,6 +6842,14 @@
       </c>
       <c r="B87" t="s" s="0">
         <v>399</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>400</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -6822,42 +6864,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -6872,26 +6914,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -6906,42 +6948,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">

--- a/rnaseq-with-probes/latest/rnaseq-with-probes.xlsx
+++ b/rnaseq-with-probes/latest/rnaseq-with-probes.xlsx
@@ -453,7 +453,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="804">
   <si>
     <t>assay_description</t>
   </si>
@@ -1733,7 +1733,7 @@
     <t>10,48,86</t>
   </si>
   <si>
-    <t>0,20-23,41-44</t>
+    <t>0,20-23,51-54</t>
   </si>
   <si>
     <t>barcode_read</t>
@@ -1769,6 +1769,9 @@
     <t>8,6</t>
   </si>
   <si>
+    <t>14-17,14,14</t>
+  </si>
+  <si>
     <t>umi_offset</t>
   </si>
   <si>
@@ -2126,6 +2129,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000250</t>
   </si>
   <si>
+    <t>Epigenome Technologies; Multiplex Droplet Paired-Tag 16 Reaction Kit; PN MDP16101</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000499</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 4 rxns; PN 1000269</t>
   </si>
   <si>
@@ -2849,7 +2858,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2026-07-17T10:23:51-07:00</t>
+    <t>2026-07-27T11:42:22-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -3090,109 +3099,109 @@
         <v>432</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="AQ1" t="s" s="1">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="AR1" t="s" s="1">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AS1" t="s" s="1">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="AT1" t="s" s="1">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="AU1" t="s" s="1">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="AV1" t="s" s="1">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="AW1" t="s" s="1">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="AX1" t="s" s="1">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="AY1" t="s" s="1">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="AZ1" t="s" s="1">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="BA1" t="s" s="1">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="2">
@@ -3200,7 +3209,7 @@
         <v>111</v>
       </c>
       <c r="BA2" t="s" s="54">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -3241,7 +3250,7 @@
       <formula1>'barcode_read'!$A$1:$A$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="R2:R1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'barcode_size'!$A$1:$A$6</formula1>
+      <formula1>'barcode_size'!$A$1:$A$7</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="S2:S1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'umi_offset'!$A$1:$A$4</formula1>
@@ -3303,7 +3312,7 @@
       <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation type="list" sqref="AK2:AK1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'library_preparation_kit'!$A$1:$A$39</formula1>
+      <formula1>'library_preparation_kit'!$A$1:$A$40</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AL2:AL1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'sample_indexing_kit'!$A$1:$A$19</formula1>
@@ -3383,7 +3392,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3413,6 +3422,11 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
         <v>237</v>
       </c>
     </row>
@@ -3438,7 +3452,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4">
@@ -3497,17 +3511,17 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5">
@@ -3532,42 +3546,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -3582,18 +3596,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -3608,18 +3622,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -3634,18 +3648,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -3660,26 +3674,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -4168,18 +4182,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -4189,319 +4203,327 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>564</v>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>566</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>567</v>
       </c>
     </row>
   </sheetData>
@@ -4516,18 +4538,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="3">
@@ -4540,130 +4562,130 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -4698,234 +4720,234 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
   </sheetData>
@@ -4972,18 +4994,18 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="7">
@@ -5020,10 +5042,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
   </sheetData>
@@ -5054,10 +5076,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4">
@@ -5070,18 +5092,18 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7">
@@ -5102,90 +5124,90 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>682</v>
+        <v>685</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>684</v>
+        <v>687</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -5200,146 +5222,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>709</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
   </sheetData>
@@ -5380,250 +5402,250 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>740</v>
+        <v>743</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>754</v>
+        <v>757</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>762</v>
+        <v>765</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>768</v>
+        <v>771</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>770</v>
+        <v>773</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>774</v>
+        <v>777</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>778</v>
+        <v>781</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>780</v>
+        <v>783</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>784</v>
+        <v>787</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>786</v>
+        <v>789</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>790</v>
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -5818,16 +5840,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="2">
@@ -5835,13 +5857,13 @@
         <v>111</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>800</v>
+        <v>803</v>
       </c>
     </row>
   </sheetData>

--- a/rnaseq-with-probes/latest/rnaseq-with-probes.xlsx
+++ b/rnaseq-with-probes/latest/rnaseq-with-probes.xlsx
@@ -65,10 +65,10 @@
     </comment>
     <comment ref="C1" authorId="1">
       <text>
-        <t>A locally assigned identifier provided by the data provider for the dataset. It
-is used to reference an external metadata record that may be maintained
-independently, enabling traceability and supporting provenance tracking.
-Example: Visium_9OLC_A4_S1</t>
+        <t>An identifier assigned by the data provider to reference an external metadata
+record for the dataset. The external record may be maintained independently and
+can support dataset traceability and provenance tracking. Leave this field empty
+if no such identifier exists.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="1">
@@ -453,7 +453,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="815">
   <si>
     <t>assay_description</t>
   </si>
@@ -1436,6 +1436,12 @@
     <t>https://identifiers.org/RRID:SCR_027072</t>
   </si>
   <si>
+    <t>iScan System</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_016388</t>
+  </si>
+  <si>
     <t>Opera Phenix HCS</t>
   </si>
   <si>
@@ -1715,12 +1721,18 @@
     <t>0</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
+    <t>0,14</t>
+  </si>
+  <si>
     <t>1,27</t>
   </si>
   <si>
@@ -1763,12 +1775,15 @@
     <t>40</t>
   </si>
   <si>
+    <t>8,6</t>
+  </si>
+  <si>
+    <t>10,10</t>
+  </si>
+  <si>
     <t>8,8,8</t>
   </si>
   <si>
-    <t>8,6</t>
-  </si>
-  <si>
     <t>14-17,14,14</t>
   </si>
   <si>
@@ -2282,6 +2297,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000463</t>
   </si>
   <si>
+    <t>Illumina; NextSeq 1000/2000 P2 XLEAP-SBS Reagent Kit (100 Cycles); PN 20100987</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000503</t>
+  </si>
+  <si>
     <t>Illumina; NovaSeq X Series 1.5B Reagent Kit (300 Cycle); PN 20104705</t>
   </si>
   <si>
@@ -2606,6 +2627,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000368</t>
   </si>
   <si>
+    <t>10x Genomics; Chromium Next GEM Chip J Single Cell Kit, 16 rxns; PN 1000230</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000263</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 16 rxns; PN 1000127</t>
   </si>
   <si>
@@ -2636,6 +2663,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000325</t>
   </si>
   <si>
+    <t>10x Genomics; Chromium Next GEM Chip J Single Cell Kit, 48 rxns; PN 1000234</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000262</t>
+  </si>
+  <si>
     <t>10x Genomics; GEM-X Flex Gene Expression Chip Kit, 4 chips; PN 1000791</t>
   </si>
   <si>
@@ -2858,7 +2891,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2026-07-27T11:42:22-07:00</t>
+    <t>2026-08-17T08:18:06-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -3072,136 +3105,136 @@
         <v>228</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="AQ1" t="s" s="1">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="AR1" t="s" s="1">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="AS1" t="s" s="1">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="AT1" t="s" s="1">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="AU1" t="s" s="1">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="AV1" t="s" s="1">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AW1" t="s" s="1">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="AX1" t="s" s="1">
-        <v>732</v>
+        <v>743</v>
       </c>
       <c r="AY1" t="s" s="1">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="AZ1" t="s" s="1">
-        <v>794</v>
+        <v>805</v>
       </c>
       <c r="BA1" t="s" s="1">
-        <v>795</v>
+        <v>806</v>
       </c>
     </row>
     <row r="2">
@@ -3209,7 +3242,7 @@
         <v>111</v>
       </c>
       <c r="BA2" t="s" s="54">
-        <v>796</v>
+        <v>807</v>
       </c>
     </row>
   </sheetData>
@@ -3227,7 +3260,7 @@
       <formula1>'acquisition_instrument_vendor'!$A$1:$A$33</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I2:I1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'acquisition_instrument_model'!$A$1:$A$88</formula1>
+      <formula1>'acquisition_instrument_model'!$A$1:$A$89</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="J2:J1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
       <formula1>0</formula1>
@@ -3244,13 +3277,13 @@
       <formula1>'time_since_acquisition_instrume'!$A$1:$A$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="P2:P1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'barcode_offset'!$A$1:$A$9</formula1>
+      <formula1>'barcode_offset'!$A$1:$A$11</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="Q2:Q1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'barcode_read'!$A$1:$A$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="R2:R1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'barcode_size'!$A$1:$A$7</formula1>
+      <formula1>'barcode_size'!$A$1:$A$8</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="S2:S1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'umi_offset'!$A$1:$A$4</formula1>
@@ -3325,7 +3358,7 @@
       <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation type="list" sqref="AP2:AP1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'sequencing_reagent_kit'!$A$1:$A$29</formula1>
+      <formula1>'sequencing_reagent_kit'!$A$1:$A$30</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AT2:AT1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'preparation_instrument_vendor'!$A$1:$A$11</formula1>
@@ -3334,7 +3367,7 @@
       <formula1>'preparation_instrument_model'!$A$1:$A$19</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AV2:AV1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'preparation_instrument_kit'!$A$1:$A$18</formula1>
+      <formula1>'preparation_instrument_kit'!$A$1:$A$20</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" sqref="AW2:AW1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-3.4028235E38</formula1>
@@ -3363,10 +3396,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2">
@@ -3379,10 +3412,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -3392,41 +3425,46 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
         <v>237</v>
       </c>
     </row>
@@ -3442,17 +3480,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4">
@@ -3472,10 +3510,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2">
@@ -3488,10 +3526,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -3506,27 +3544,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6">
@@ -3546,42 +3584,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -3596,18 +3634,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -3622,18 +3660,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -3648,18 +3686,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -3674,26 +3712,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -4182,18 +4220,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -4208,322 +4246,322 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>533</v>
+        <v>538</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>545</v>
+        <v>550</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>555</v>
+        <v>560</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>559</v>
+        <v>564</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>565</v>
+        <v>570</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>567</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>
@@ -4538,18 +4576,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>570</v>
+        <v>575</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3">
@@ -4562,130 +4600,130 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>574</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>576</v>
+        <v>581</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>578</v>
+        <v>583</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>582</v>
+        <v>587</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>586</v>
+        <v>591</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>590</v>
+        <v>595</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>594</v>
+        <v>599</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>598</v>
+        <v>603</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -4715,239 +4753,247 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>608</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>612</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>622</v>
+        <v>627</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>628</v>
+        <v>633</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>630</v>
+        <v>635</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>632</v>
+        <v>637</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>638</v>
+        <v>643</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>640</v>
+        <v>645</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>546</v>
+        <v>646</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>547</v>
+        <v>647</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>641</v>
+        <v>551</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>642</v>
+        <v>552</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>644</v>
+        <v>649</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>646</v>
+        <v>651</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>648</v>
+        <v>653</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>652</v>
+        <v>657</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>654</v>
+        <v>659</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>656</v>
+        <v>661</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>658</v>
+        <v>663</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>660</v>
+        <v>665</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>662</v>
+        <v>667</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>668</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -4994,18 +5040,18 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>670</v>
+        <v>677</v>
       </c>
     </row>
     <row r="7">
@@ -5042,10 +5088,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>672</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>
@@ -5076,10 +5122,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>675</v>
+        <v>682</v>
       </c>
     </row>
     <row r="4">
@@ -5092,18 +5138,18 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>677</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="7">
@@ -5116,98 +5162,98 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>679</v>
+        <v>686</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>681</v>
+        <v>688</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>685</v>
+        <v>692</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>689</v>
+        <v>696</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>693</v>
+        <v>700</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>697</v>
+        <v>704</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>699</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -5217,151 +5263,167 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>702</v>
+        <v>709</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>704</v>
+        <v>711</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>708</v>
+        <v>715</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>710</v>
+        <v>717</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>712</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>714</v>
+        <v>721</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>716</v>
+        <v>723</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>718</v>
+        <v>725</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>556</v>
+        <v>726</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>557</v>
+        <v>727</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>719</v>
+        <v>561</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>720</v>
+        <v>562</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>722</v>
+        <v>729</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>724</v>
+        <v>731</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>726</v>
+        <v>733</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>728</v>
+        <v>735</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>730</v>
+        <v>737</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>738</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>740</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>741</v>
       </c>
     </row>
   </sheetData>
@@ -5376,18 +5438,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -5402,250 +5464,250 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>735</v>
+        <v>746</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>737</v>
+        <v>748</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>739</v>
+        <v>750</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>741</v>
+        <v>752</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>743</v>
+        <v>754</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>744</v>
+        <v>755</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>745</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>747</v>
+        <v>758</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>749</v>
+        <v>760</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>750</v>
+        <v>761</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>751</v>
+        <v>762</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>753</v>
+        <v>764</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>755</v>
+        <v>766</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>756</v>
+        <v>767</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>757</v>
+        <v>768</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>759</v>
+        <v>770</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>760</v>
+        <v>771</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>761</v>
+        <v>772</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>762</v>
+        <v>773</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>763</v>
+        <v>774</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>764</v>
+        <v>775</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>765</v>
+        <v>776</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>766</v>
+        <v>777</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>767</v>
+        <v>778</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>768</v>
+        <v>779</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>769</v>
+        <v>780</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>771</v>
+        <v>782</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>772</v>
+        <v>783</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>773</v>
+        <v>784</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>774</v>
+        <v>785</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>775</v>
+        <v>786</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>777</v>
+        <v>788</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>779</v>
+        <v>790</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>780</v>
+        <v>791</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>781</v>
+        <v>792</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>782</v>
+        <v>793</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>783</v>
+        <v>794</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>784</v>
+        <v>795</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>785</v>
+        <v>796</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>786</v>
+        <v>797</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>787</v>
+        <v>798</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>789</v>
+        <v>800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>790</v>
+        <v>801</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>791</v>
+        <v>802</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>792</v>
+        <v>803</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>793</v>
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -5840,16 +5902,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>798</v>
+        <v>809</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>800</v>
+        <v>811</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>802</v>
+        <v>813</v>
       </c>
     </row>
     <row r="2">
@@ -5857,13 +5919,13 @@
         <v>111</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>799</v>
+        <v>810</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>801</v>
+        <v>812</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>803</v>
+        <v>814</v>
       </c>
     </row>
   </sheetData>
@@ -6167,7 +6229,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6708,15 +6770,15 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="B69" t="s" s="0">
         <v>365</v>
@@ -6740,18 +6802,18 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>194</v>
+        <v>370</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>195</v>
+        <v>371</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>370</v>
+        <v>194</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>371</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74">
@@ -6872,6 +6934,14 @@
       </c>
       <c r="B88" t="s" s="0">
         <v>401</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>402</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -6886,42 +6956,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -6936,26 +7006,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -6965,51 +7035,61 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
         <v>237</v>
       </c>
     </row>
